--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0200.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0200.xlsx
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Lần sau ta sẽ nhắn ngươi.</t>
+          <t>Lần sau tao sẽ nhắn mày.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Ta phải công nhận ngươi có công.</t>
+          <t>Tao phải công nhận mày có công.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Như ta đã nói trước đây, ngươi cũng giống như bao người khác thôi. Ngươi không cần phải gánh vác nhiều hơn phần của mình... dù ngươi lúc nào cũng làm thế.</t>
+          <t>Như tao đã nói trước đây, mày cũng giống như bao người khác thôi. Mày không cần phải gánh vác nhiều hơn phần của mình... dù mày lúc nào cũng làm thế.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Ta đã có linh cảm sẽ gặp ngươi ở đây.</t>
+          <t>Tao đã có linh cảm sẽ gặp mày ở đây.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Có chuyện gì mà cậu lại đến đây?</t>
+          <t>Có chuyện gì mà bạn lại đến đây?</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Ta nhớ đã thấy cái này trong thực đơn đâu đó rồi.</t>
+          <t>Tao nhớ đã thấy cái này trong thực đơn đâu đó rồi.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Thật sao? Nếu bị bắt, đừng có lôi tên ta vào nhé!</t>
+          <t>Thật sao? Nếu bị bắt, đừng có lôi tên tao vào nhé!</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Này, đừng có đổ lỗi cho ta như thế. Ta còn bao nhiêu điểm tốt nữa chứ? Cậu có thể chọn bất kỳ cái nào mà, biết không...</t>
+          <t>Này, đừng có đổ lỗi cho tao như thế. Tao còn bao nhiêu điểm tốt nữa chứ? Cậu có thể chọn bất kỳ cái nào mà, biết không...</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Thôi, đủ rồi. Thử mấy viên Jiggly-Giggly Tất cả-Flavor Beans đi. Nghe nói mỗi viên có một hương vị riêng biệt đấy.</t>
+          <t>Thôi, đủ rồi. Thử mấy viên Jiggly-Giggly All-Flavor Beans đi. Nghe nói mỗi viên có một hương vị riêng biệt đấy.</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Tuyệt! Ở lại chơi một lát đi? Ta phải kể cho ngươi nghe hết mấy drama mới nhất ở trường đấy, haha…</t>
+          <t>Tuyệt! Ở lại chơi một lát đi? Tao phải kể cho mày nghe hết mấy drama mới nhất ở trường đấy, haha…</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Ta cứ nghĩ là sẽ gặp lại ngươi thôi.</t>
+          <t>Tao cứ nghĩ là sẽ gặp lại mày thôi.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Lúc đầu, ta chỉ là một hạt bụi nhỏ bé trôi dạt trong khoảng không tối tăm, tĩnh lặng của vũ trụ.</t>
+          <t>Lúc đầu, tao chỉ là một hạt bụi nhỏ bé trôi dạt trong khoảng không tối tăm, tĩnh lặng của vũ trụ.</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>À, vậy à... Biết rằng cậu vẫn nghĩ về ta dưới bầu trời này... Ta thấy vui lắm.</t>
+          <t>À, vậy à... Biết rằng cậu vẫn nghĩ về tao dưới bầu trời này... Tao thấy vui lắm.</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Ừ, mình sẽ giữ liên lạc nhé—À, bạn ta đến rồi. Hẹn nói chuyện sau nhé, mẹ. Được rồi, tạm biệt.</t>
+          <t>Ừ, mình sẽ giữ liên lạc nhé—À, bạn tao đến rồi. Hẹn nói chuyện sau nhé, mẹ. Được rồi, tạm biệt.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Mỗi khi cô ấy gọi điện hồi đó, ta chỉ nói "Ta ổn" hoặc "Mọi thứ đều ổn."</t>
+          <t>Mỗi khi cô ấy gọi điện hồi đó, tao chỉ nói "Tao ổn" hoặc "Mọi thứ đều ổn."</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Cậu cần phải thay đổi thôi.</t>
+          <t>Mày cần phải thay đổi thôi.</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Như việc học hành của ta khó khăn thế nào, mệt mỏi ra sao, và còn bao nhiêu thứ ta vẫn chưa làm được...</t>
+          <t>Như việc học hành của tao khó khăn thế nào, mệt mỏi ra sao, và còn bao nhiêu thứ tao vẫn chưa làm được...</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Ừ! Và ta cũng chẳng hề chậm lại đâu.</t>
+          <t>Ừ! Và tao cũng chẳng hề chậm lại đâu.</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Ta còn quá nhiều điều muốn làm. Và ta sẽ làm hết. Từng việc một.</t>
+          <t>Tao còn quá nhiều điều muốn làm. Và tao sẽ làm hết. Từng việc một.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Tiền bối rảnh rỗi lúc nào, mình về nhà em chơi nhé?</t>
+          <t>bạn rảnh rỗi lúc nào, mình về nhà em chơi nhé?</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Ta kể với Crackle tất tần tật về cậu rồi, nó háo hức muốn gặp cậu lắm đấy!</t>
+          <t>Tao kể với Crackle tất tần tật về cậu rồi, nó háo hức muốn gặp cậu lắm đấy!</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>À, con chim kia là thú cưng của ta. Một con Kronapuff.</t>
+          <t>À, con chim kia là thú cưng của tao. Một con Kronapuff.</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Tại sao?</t>
+          <t>Sao vậy?</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>...Được rồi, được rồi, ta biết ngươi sắp nói gì rồi.</t>
+          <t>...Được rồi, được rồi, tao biết mày sắp nói gì rồi.</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Cậu vừa cướp mất lời ta nói luôn rồi.</t>
+          <t>Cậu vừa cướp mất lời tao nói luôn rồi.</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Lo là ta sẽ ngất tại bàn vì thiếu ngủ chăng?</t>
+          <t>Lo là tao sẽ ngất tại bàn vì thiếu ngủ chăng?</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Hy vọng cậu sẽ có một ngày vui vẻ và trọn vẹn, {Male=chàng trai vàng;Female=cô gái vàng} à.</t>
+          <t>Hy vọng cậu sẽ có một ngày vui vẻ và trọn vẹn, {Male=golden boy;Female=golden girl} à.</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Được thôi, sao lại không?</t>
+          <t>Được thôi, tại sao không nhỉ?</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Thật lòng, ta chưa hài lòng với trận đấu lần trước của chúng ta.</t>
+          <t>Thật lòng, tao chưa hài lòng với trận đấu lần trước của chúng ta.</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Chẳng lẽ chỉ mình ta, hay cái bóng đèn đuôi ta sáng hơn trước rồi?</t>
+          <t>Chẳng lẽ chỉ mình tao, hay cái bóng đèn đuôi tao sáng hơn trước rồi?</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Nhanh lên đi. Ta còn mấy thí nghiệm đang chờ đây.</t>
+          <t>Nhanh lên đi. Tao còn mấy thí nghiệm đang chờ đây.</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Cậu có thể tin ta sẽ bảo vệ cậu.</t>
+          <t>Cậu có thể tin tao sẽ bảo vệ cậu.</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Ta có khá nhiều kinh nghiệm làm thủy thủ, để ta giúp với. À, xin lỗi... Quên mất mình không còn làm việc ở đây nữa.</t>
+          <t>Tao có khá nhiều kinh nghiệm làm thủy thủ, để tao giúp với. À, xin lỗi... Quên mất mình không còn làm việc ở đây nữa.</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Ấn tượng! Ta chưa bao giờ nghĩ có thể dùng Pathfinder Ramp như thế này!</t>
+          <t>Ấn tượng! Tao chưa bao giờ nghĩ có thể dùng Pathfinder Ramp như thế này!</t>
         </is>
       </c>
     </row>
